--- a/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/01_RR1 - PFMEA ve Müşteri Puanlama Kuralları/EKG-PRJ-MTR-02_pfmea_ekibi_egitim_ve_yetkinlik_matrisi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/01_RR1 - PFMEA ve Müşteri Puanlama Kuralları/EKG-PRJ-MTR-02_pfmea_ekibi_egitim_ve_yetkinlik_matrisi.xlsx
@@ -785,7 +785,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-MTR-02&amp;C&amp;"Arial,Regular"&amp;11PFMEA Ekibi Eğitim ve Yetkinlik Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 04.09.2026
+Revizyon nedeni: Yetkinlik matrisi belge, uygulama kanıtı ve görev atamasını ayıracak şekilde kısaltıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -927,7 +928,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-MTR-02&amp;C&amp;"Arial,Regular"&amp;11PFMEA Ekibi Eğitim ve Yetkinlik Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 04.09.2026
+Revizyon nedeni: Yetkinlik matrisi belge, uygulama kanıtı ve görev atamasını ayıracak şekilde kısaltıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>